--- a/jpcore-r4/feature_swg45_improve_readability/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature_swg45_improve_readability/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T14:15:03+00:00</t>
+    <t>2025-06-06T06:25:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
